--- a/web/public/forms/chakgong.xlsx
+++ b/web/public/forms/chakgong.xlsx
@@ -174,7 +174,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="166" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -786,7 +786,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>현장대리인 지정신고서(재직·경력증명 포함)</t>
+          <t>현장기술자(현장대리인) 지정신고서</t>
         </is>
       </c>
       <c r="C19" s="6" t="n"/>
@@ -803,7 +803,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>공사예정공정표</t>
+          <t>공사공정예정표</t>
         </is>
       </c>
       <c r="C20" s="6" t="n"/>
@@ -820,7 +820,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>산출내역서</t>
+          <t>안전·환경 및 품질관리계획서</t>
         </is>
       </c>
       <c r="C21" s="6" t="n"/>
@@ -837,7 +837,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>착공 전 현장사진</t>
+          <t>공정별 인력 및 장비투입계획서</t>
         </is>
       </c>
       <c r="C22" s="6" t="n"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>안전관리계획서·품질관리계획서(대상 공사만)</t>
+          <t>착공 전 현장사진</t>
         </is>
       </c>
       <c r="C23" s="6" t="n"/>
@@ -888,7 +888,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>건설공사 보험증권(해당 공사만)</t>
+          <t>그 밖에 발주기관이 지정한 서류</t>
         </is>
       </c>
       <c r="C25" s="6" t="n"/>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>현장대리인 지정신고서(재직·경력증명 포함)</t>
+          <t>현장기술자(현장대리인) 지정신고서</t>
         </is>
       </c>
       <c r="C19" s="6" t="n"/>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>공사예정공정표</t>
+          <t>공사공정예정표</t>
         </is>
       </c>
       <c r="C20" s="6" t="n"/>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>산출내역서</t>
+          <t>안전·환경 및 품질관리계획서</t>
         </is>
       </c>
       <c r="C21" s="6" t="n"/>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>착공 전 현장사진</t>
+          <t>공정별 인력 및 장비투입계획서</t>
         </is>
       </c>
       <c r="C22" s="6" t="n"/>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>안전관리계획서·품질관리계획서(대상 공사만)</t>
+          <t>착공 전 현장사진</t>
         </is>
       </c>
       <c r="C23" s="6" t="n"/>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>건설공사 보험증권(해당 공사만)</t>
+          <t>그 밖에 발주기관이 지정한 서류</t>
         </is>
       </c>
       <c r="C25" s="6" t="n"/>

--- a/web/public/forms/chakgong.xlsx
+++ b/web/public/forms/chakgong.xlsx
@@ -604,7 +604,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
@@ -1078,7 +1078,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="E1" s="25" t="inlineStr">

--- a/web/public/forms/chakgong.xlsx
+++ b/web/public/forms/chakgong.xlsx
@@ -8,11 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="착공계" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'착공계'!$A$1:$G$36</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$G$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -149,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -220,9 +218,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -677,10 +672,7 @@
       <c r="B9" s="6" t="n"/>
       <c r="C9" s="9" t="n"/>
       <c r="D9" s="6" t="n"/>
-      <c r="E9" s="10">
-        <f>C9</f>
-        <v/>
-      </c>
+      <c r="E9" s="10" t="n"/>
       <c r="F9" s="6" t="n"/>
       <c r="G9" s="6" t="n"/>
     </row>
@@ -691,10 +683,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n"/>
-      <c r="C10" s="11">
-        <f>IF(OR(C11="",C12=""),"",TEXT(C11,"yyyy. m. d.")&amp;" ~ "&amp;TEXT(C12,"yyyy. m. d.")&amp;" ("&amp;TEXT(C12-C11+1,"#,##0")&amp;"일)")</f>
-        <v/>
-      </c>
+      <c r="C10" s="11" t="n"/>
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="6" t="n"/>
       <c r="F10" s="6" t="n"/>
@@ -740,17 +729,11 @@
       <c r="G13" s="6" t="n"/>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="12">
-        <f>IF(OR(C11="",C8=""),"",IF(C11&lt;C8,"⚠ 착공일이 계약일보다 앞섭니다 — 날짜를 확인하세요.",IF(AND(C12&lt;&gt;"",C12&lt;C11),"⚠ 준공예정일이 착공일보다 앞섭니다.","")))</f>
-        <v/>
-      </c>
+      <c r="A14" s="12" t="n"/>
     </row>
     <row r="15" ht="6" customHeight="1"/>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="13">
-        <f>"위 공사를 계약조건에 따라 "&amp;IF(ISNUMBER(C11),TEXT(C11,"yyyy년 m월 d일"),"     년     월     일")&amp;" 착공하였기에 관계 서류를 붙여 신고합니다."</f>
-        <v/>
-      </c>
+      <c r="A16" s="13" t="n"/>
     </row>
     <row r="17" ht="8" customHeight="1"/>
     <row r="18" ht="22" customHeight="1">
@@ -980,6 +963,7 @@
         </is>
       </c>
     </row>
+    <row r="37"/>
     <row r="38" ht="34" customHeight="1">
       <c r="A38" s="24" t="inlineStr">
         <is>
@@ -1054,524 +1038,4 @@
   <pageMargins left="0.45" right="0.35" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:G38"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="E1" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="6" customHeight="1"/>
-    <row r="3" ht="40" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>착  공  계</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>(착공신고서)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="10" customHeight="1"/>
-    <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>공  사  명</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>가나지구 배수로 정비공사</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-    </row>
-    <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>계 약 번 호</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>제2026-0312호</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>계 약 일 자</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="8" t="n">
-        <v>46083</v>
-      </c>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="6" t="n"/>
-    </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>계 약 금 액</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="9" t="n">
-        <v>963241000</v>
-      </c>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="10">
-        <f>C9</f>
-        <v/>
-      </c>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>공 사 기 간</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="11">
-        <f>IF(OR(C11="",C12=""),"",TEXT(C11,"yyyy. m. d.")&amp;" ~ "&amp;TEXT(C12,"yyyy. m. d.")&amp;" ("&amp;TEXT(C12-C11+1,"#,##0")&amp;"일)")</f>
-        <v/>
-      </c>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-    </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>착  공  일</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="8" t="n">
-        <v>46090</v>
-      </c>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
-    </row>
-    <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>준공예정일</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="8" t="n">
-        <v>46387</v>
-      </c>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="n"/>
-    </row>
-    <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>현 장 위 치</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>가나시 다라동 123-4 일원</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="12">
-        <f>IF(OR(C11="",C8=""),"",IF(C11&lt;C8,"⚠ 착공일이 계약일보다 앞섭니다 — 날짜를 확인하세요.",IF(AND(C12&lt;&gt;"",C12&lt;C11),"⚠ 준공예정일이 착공일보다 앞섭니다.","")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="6" customHeight="1"/>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="13">
-        <f>"위 공사를 계약조건에 따라 "&amp;IF(ISNUMBER(C11),TEXT(C11,"yyyy년 m월 d일"),"     년     월     일")&amp;" 착공하였기에 관계 서류를 붙여 신고합니다."</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="8" customHeight="1"/>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t>번호</t>
-        </is>
-      </c>
-      <c r="B18" s="14" t="inlineStr">
-        <is>
-          <t>붙 임 서 류</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="14" t="inlineStr">
-        <is>
-          <t>부수</t>
-        </is>
-      </c>
-      <c r="G18" s="14" t="inlineStr">
-        <is>
-          <t>비 고</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="21" customHeight="1">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>현장기술자(현장대리인) 지정신고서</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>1부</t>
-        </is>
-      </c>
-      <c r="G19" s="17" t="n"/>
-    </row>
-    <row r="20" ht="21" customHeight="1">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>공사공정예정표</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>1부</t>
-        </is>
-      </c>
-      <c r="G20" s="17" t="n"/>
-    </row>
-    <row r="21" ht="21" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>안전·환경 및 품질관리계획서</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>1부</t>
-        </is>
-      </c>
-      <c r="G21" s="17" t="n"/>
-    </row>
-    <row r="22" ht="21" customHeight="1">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>공정별 인력 및 장비투입계획서</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>1부</t>
-        </is>
-      </c>
-      <c r="G22" s="17" t="n"/>
-    </row>
-    <row r="23" ht="21" customHeight="1">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>착공 전 현장사진</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="6" t="n"/>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="16" t="inlineStr">
-        <is>
-          <t>1부</t>
-        </is>
-      </c>
-      <c r="G23" s="17" t="n"/>
-    </row>
-    <row r="24" ht="21" customHeight="1">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>산재·고용보험 가입증명원</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="n"/>
-      <c r="D24" s="6" t="n"/>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="16" t="inlineStr">
-        <is>
-          <t>1부</t>
-        </is>
-      </c>
-      <c r="G24" s="17" t="n"/>
-    </row>
-    <row r="25" ht="21" customHeight="1">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>그 밖에 발주기관이 지정한 서류</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="6" t="n"/>
-      <c r="E25" s="6" t="n"/>
-      <c r="F25" s="16" t="n"/>
-      <c r="G25" s="17" t="inlineStr">
-        <is>
-          <t>해당 없음</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="21" customHeight="1">
-      <c r="A26" s="15" t="inlineStr"/>
-      <c r="B26" s="7" t="n"/>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="16" t="n"/>
-      <c r="G26" s="17" t="n"/>
-    </row>
-    <row r="27" ht="21" customHeight="1">
-      <c r="A27" s="15" t="inlineStr"/>
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="16" t="n"/>
-      <c r="G27" s="17" t="n"/>
-    </row>
-    <row r="28" ht="10" customHeight="1"/>
-    <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="18" t="n">
-        <v>46090</v>
-      </c>
-    </row>
-    <row r="30" ht="6" customHeight="1"/>
-    <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="19" t="inlineStr"/>
-      <c r="C31" s="20" t="inlineStr">
-        <is>
-          <t>주소</t>
-        </is>
-      </c>
-      <c r="D31" s="21" t="inlineStr">
-        <is>
-          <t>가나시 마바로 45, 2층</t>
-        </is>
-      </c>
-      <c r="G31" s="22" t="inlineStr"/>
-    </row>
-    <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="19" t="inlineStr"/>
-      <c r="C32" s="20" t="inlineStr">
-        <is>
-          <t>상호</t>
-        </is>
-      </c>
-      <c r="D32" s="21" t="inlineStr">
-        <is>
-          <t>예시건설(주)</t>
-        </is>
-      </c>
-      <c r="G32" s="22" t="inlineStr"/>
-    </row>
-    <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="19" t="inlineStr"/>
-      <c r="C33" s="20" t="inlineStr">
-        <is>
-          <t>대표자</t>
-        </is>
-      </c>
-      <c r="D33" s="21" t="inlineStr">
-        <is>
-          <t>홍길동</t>
-        </is>
-      </c>
-      <c r="G33" s="22" t="inlineStr">
-        <is>
-          <t>(인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="19" t="inlineStr"/>
-      <c r="C34" s="20" t="inlineStr">
-        <is>
-          <t>현장대리인</t>
-        </is>
-      </c>
-      <c r="D34" s="21" t="inlineStr">
-        <is>
-          <t>김철수</t>
-        </is>
-      </c>
-      <c r="G34" s="22" t="inlineStr">
-        <is>
-          <t>(인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="10" customHeight="1"/>
-    <row r="36" ht="26" customHeight="1">
-      <c r="A36" s="23" t="inlineStr">
-        <is>
-          <t>가나시장 귀하</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="19.5" customHeight="1">
-      <c r="A38" s="24" t="inlineStr">
-        <is>
-          <t>이 시트는 작성 예시입니다(가상의 공사). 실제로는 앞 시트에 적으세요.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="44">
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A38:G38"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="E1:G1"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.45" right="0.35" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/web/public/forms/chakgong.xlsx
+++ b/web/public/forms/chakgong.xlsx
@@ -599,7 +599,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
